--- a/data/credit-cards.xlsx
+++ b/data/credit-cards.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -453,53 +453,24 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3420</v>
+        <v>3500</v>
       </c>
       <c r="F2">
-        <v>24.99</v>
+        <v>22.99</v>
       </c>
       <c r="G2">
-        <v>3420</v>
+        <v>3500</v>
       </c>
       <c r="H2" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="I2" t="str">
-        <v>Paid in full monthly. Points earning card.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>chase-sapphire</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Chase Sapphire Reserve</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Revolving</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>1850</v>
-      </c>
-      <c r="F3">
-        <v>22.49</v>
-      </c>
-      <c r="G3">
-        <v>1850</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Travel rewards card. Paid in full.</v>
+        <v>Paid in full monthly. Dining &amp; grocery rewards. SF restaurant spending.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/credit-cards.xlsx
+++ b/data/credit-cards.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -441,10 +441,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>amex-gold</v>
+        <v>amex-plat</v>
       </c>
       <c r="B2" t="str">
-        <v>Amex Gold</v>
+        <v>Amex Platinum</v>
       </c>
       <c r="C2" t="str">
         <v>Revolving</v>
@@ -453,24 +453,53 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3500</v>
+        <v>4200</v>
       </c>
       <c r="F2">
-        <v>22.99</v>
+        <v>24.99</v>
       </c>
       <c r="G2">
-        <v>3500</v>
+        <v>4200</v>
       </c>
       <c r="H2" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="I2" t="str">
-        <v>Paid in full monthly. Dining &amp; grocery rewards. SF restaurant spending.</v>
+        <v>Paid in full monthly. Travel &amp; dining rewards.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>chase-sapphire</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Chase Sapphire Reserve</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Revolving</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>2800</v>
+      </c>
+      <c r="F3">
+        <v>22.49</v>
+      </c>
+      <c r="G3">
+        <v>2800</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Travel rewards card. Paid in full.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/credit-cards.xlsx
+++ b/data/credit-cards.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -441,10 +441,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>amex-plat</v>
+        <v>amex-gold</v>
       </c>
       <c r="B2" t="str">
-        <v>Amex Platinum</v>
+        <v>Amex Gold</v>
       </c>
       <c r="C2" t="str">
         <v>Revolving</v>
@@ -453,53 +453,24 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="F2">
-        <v>24.99</v>
+        <v>22.99</v>
       </c>
       <c r="G2">
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="H2" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="I2" t="str">
-        <v>Paid in full monthly. Travel &amp; dining rewards.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>chase-sapphire</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Chase Sapphire Reserve</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Revolving</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>2800</v>
-      </c>
-      <c r="F3">
-        <v>22.49</v>
-      </c>
-      <c r="G3">
-        <v>2800</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Travel rewards card. Paid in full.</v>
+        <v>Paid in full monthly. Dining &amp; grocery rewards. SF restaurant spending.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
 </file>